--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/13_Anotacijos_logai/13_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/13_Anotacijos_logai/13_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\13_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47B7643-034B-4A3A-B528-2B0A2CBC4899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BDFA985-2414-41F7-9CF3-8D3AB8694C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,6 +168,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -717,7 +718,7 @@
       <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="F2" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="4"/>
@@ -750,7 +751,7 @@
       <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="b">
+      <c r="F3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -784,7 +785,7 @@
       <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="F4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -816,7 +817,7 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="F5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -850,7 +851,7 @@
       <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="b">
+      <c r="F6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="4"/>
@@ -881,7 +882,7 @@
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="b">
+      <c r="F7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3"/>
